--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486963_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486963_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2849</v>
+        <v>6.5083</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9886</v>
+        <v>6.4196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2962</v>
+        <v>0.0887</v>
       </c>
       <c r="G2" t="n">
         <v>3.0414</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2516</v>
+        <v>1.4751</v>
       </c>
       <c r="T2" t="n">
-        <v>2.704</v>
+        <v>1.135</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5476</v>
+        <v>0.3401</v>
       </c>
       <c r="V2" t="n">
         <v>0.3491</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2257</v>
+        <v>1.4645</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2136</v>
+        <v>0.4228</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0121</v>
+        <v>1.0417</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0997</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0934</v>
+        <v>0.3322</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2517</v>
+        <v>0.4609</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1583</v>
+        <v>-0.1287</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8589</v>
+        <v>1.3056</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1419</v>
+        <v>1.0549</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0008</v>
+        <v>0.2506</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7685</v>
+        <v>-1.9035</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4869</v>
+        <v>-1.2586</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2816</v>
+        <v>-0.6449</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3804</v>
+        <v>-0.0473</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3149</v>
+        <v>-0.3756</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0655</v>
+        <v>0.3284</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1489</v>
+        <v>-1.8562</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8017</v>
+        <v>-0.883</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3472</v>
+        <v>-0.9732</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4374</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2289</v>
+        <v>0.0223</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9145</v>
+        <v>0.1741</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3144</v>
+        <v>-0.1519</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4189</v>
+        <v>3.1868</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4189</v>
+        <v>3.1868</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8048</v>
+        <v>1.0534</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9734</v>
+        <v>0.4082</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7782</v>
+        <v>0.6451</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5538</v>
+        <v>-0.7685</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4802</v>
+        <v>-0.4869</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0736</v>
+        <v>-0.2816</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.9147</v>
+        <v>0.3804</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3149</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2368</v>
+        <v>0.0655</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3609</v>
+        <v>-1.1489</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1977</v>
+        <v>-0.8017</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1632</v>
+        <v>-0.3472</v>
       </c>
       <c r="P5" t="n">
         <v>1.4374</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2231</v>
+        <v>-1.0344</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9413</v>
+        <v>-0.3643</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7183</v>
+        <v>-0.6701</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6982</v>
+        <v>1.4189</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.5991</v>
       </c>
       <c r="E6" t="n">
-        <v>0.466</v>
+        <v>1.7621</v>
       </c>
       <c r="F6" t="n">
-        <v>0.221</v>
+        <v>-1.163</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9035</v>
+        <v>1.1734</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2586</v>
+        <v>-0.2079</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6449</v>
+        <v>1.3813</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0473</v>
+        <v>1.7614</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3756</v>
+        <v>0.5908</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3284</v>
+        <v>1.1706</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8562</v>
+        <v>-0.588</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.883</v>
+        <v>-0.7987</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9732</v>
+        <v>0.2107</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-1.4306</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4147</v>
+        <v>-0.1861</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1815</v>
+        <v>-1.2445</v>
       </c>
       <c r="V6" t="n">
-        <v>3.1868</v>
+        <v>0.2402</v>
       </c>
       <c r="W6" t="n">
-        <v>3.1868</v>
+        <v>1.4189</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CLIMENT FIGUERES</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4357</v>
+        <v>0.3163</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0464</v>
+        <v>-1.6397</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3893</v>
+        <v>1.956</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3698</v>
+        <v>-1.5538</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3698</v>
+        <v>-0.4802</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.0736</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0195</v>
+        <v>-1.9147</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0195</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.2368</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3893</v>
+        <v>0.3609</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3893</v>
+        <v>0.1977</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1632</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.4374</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0659</v>
+        <v>-0.2654</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0659</v>
+        <v>0.275</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.5404</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.441</v>
+        <v>-0.0602</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1073</v>
+        <v>0.5736</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5484</v>
+        <v>-0.6338</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1734</v>
+        <v>1.1971</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2079</v>
+        <v>3.273</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3813</v>
+        <v>-2.076</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7614</v>
+        <v>3.1115</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5908</v>
+        <v>3.7958</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1706</v>
+        <v>-0.6843</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.588</v>
+        <v>-1.9144</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7987</v>
+        <v>-0.5228</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2107</v>
+        <v>-1.3917</v>
       </c>
       <c r="P8" t="n">
-        <v>0.616</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2321</v>
+        <v>-3.2855</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.4707</v>
+        <v>0.6257</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8409</v>
+        <v>0.5074</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6298</v>
+        <v>0.1183</v>
       </c>
       <c r="V8" t="n">
+        <v>-0.2402</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.2402</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.4189</v>
-      </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>J. CLIMENT FIGUERES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.708</v>
+        <v>-0.3698</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1535</v>
+        <v>0.0195</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5545</v>
+        <v>-0.3893</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2037</v>
+        <v>-0.3698</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2619</v>
+        <v>-0.3698</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4656</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9004</v>
+        <v>0.0195</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4019</v>
+        <v>0.0195</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3024</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6967</v>
+        <v>-0.3893</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8599</v>
+        <v>-0.3893</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1632</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0272</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5272</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0002</v>
+        <v>-0.6718</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2584</v>
+        <v>-0.0877</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7417</v>
+        <v>-0.5841</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1704</v>
+        <v>0.2037</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4507</v>
+        <v>-1.2619</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6211</v>
+        <v>1.4656</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4089</v>
+        <v>0.9004</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1854</v>
+        <v>-0.4019</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2234</v>
+        <v>1.3024</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2385</v>
+        <v>-0.6967</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6362</v>
+        <v>-0.8599</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.1632</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6714</v>
+        <v>-0.5182</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4333</v>
+        <v>0.0386</v>
       </c>
       <c r="U10" t="n">
-        <v>0.238</v>
+        <v>-0.5569</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2259</v>
+        <v>-1.1786</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0472</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.1786</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2174</v>
+        <v>-1.7546</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6429</v>
+        <v>-3.0495</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5746</v>
+        <v>1.2948</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1971</v>
+        <v>-2.88</v>
       </c>
       <c r="H11" t="n">
-        <v>3.273</v>
+        <v>-1.9141</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.076</v>
+        <v>-0.9659</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1115</v>
+        <v>-2.686</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7958</v>
+        <v>-1.2779</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6843</v>
+        <v>-1.4081</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9144</v>
+        <v>-0.194</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5228</v>
+        <v>-0.6362</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3917</v>
+        <v>0.4422</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2855</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5315</v>
+        <v>-1.2853</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7091</v>
+        <v>-0.5154</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1776</v>
+        <v>-0.7699</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2372</v>
+        <v>-1.9102</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3246</v>
+        <v>-0.9907</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0873</v>
+        <v>-0.9196</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.88</v>
+        <v>0.1704</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9141</v>
+        <v>-0.4507</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9659</v>
+        <v>0.6211</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.686</v>
+        <v>1.4089</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2779</v>
+        <v>0.1854</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4081</v>
+        <v>1.2234</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.194</v>
+        <v>-1.2385</v>
       </c>
       <c r="N12" t="n">
         <v>-0.6362</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4422</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2588</v>
+        <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7679</v>
+        <v>0.7613</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7905</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9774</v>
+        <v>0.0602</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1786</v>
+        <v>-2.2259</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1786</v>
+        <v>-1.0472</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.821800000000001</v>
+        <v>6.480600000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2344</v>
+        <v>4.893099999999999</v>
       </c>
       <c r="F13" t="n">
         <v>1.5871</v>
@@ -1438,13 +1438,13 @@
         <v>1.8161</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.605500000000001</v>
+        <v>-3.605499999999999</v>
       </c>
       <c r="J13" t="n">
         <v>9.028700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>7.8868</v>
+        <v>7.886800000000001</v>
       </c>
       <c r="L13" t="n">
         <v>1.142</v>
@@ -1459,7 +1459,7 @@
         <v>-4.7476</v>
       </c>
       <c r="P13" t="n">
-        <v>6.1604</v>
+        <v>6.160399999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.3473</v>
@@ -1468,19 +1468,19 @@
         <v>19.5076</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9762</v>
+        <v>-1.3173</v>
       </c>
       <c r="T13" t="n">
-        <v>1.567500000000001</v>
+        <v>2.2263</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.5437</v>
+        <v>-3.543799999999999</v>
       </c>
       <c r="V13" t="n">
         <v>3.427099999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.985499999999999</v>
+        <v>6.985499999999998</v>
       </c>
       <c r="X13" t="n">
         <v>-3.5583</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.935</v>
+        <v>6.588</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9439</v>
+        <v>6.5255</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0089</v>
+        <v>0.0625</v>
       </c>
       <c r="G14" t="n">
         <v>4.6122</v>
@@ -1546,13 +1546,13 @@
         <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1441</v>
+        <v>0.7972</v>
       </c>
       <c r="T14" t="n">
-        <v>1.193</v>
+        <v>0.7746</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0489</v>
+        <v>0.0226</v>
       </c>
       <c r="V14" t="n">
         <v>1.1786</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5199</v>
+        <v>3.0875</v>
       </c>
       <c r="E15" t="n">
-        <v>3.543</v>
+        <v>3.2292</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0231</v>
+        <v>-0.1417</v>
       </c>
       <c r="G15" t="n">
         <v>2.9941</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9981</v>
+        <v>0.5657</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0227</v>
+        <v>0.7088</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0246</v>
+        <v>-0.1431</v>
       </c>
       <c r="V15" t="n">
         <v>0.3491</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3835</v>
+        <v>1.7653</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3513</v>
+        <v>0.2467</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0322</v>
+        <v>1.5186</v>
       </c>
       <c r="G16" t="n">
         <v>0.3897</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.191</v>
+        <v>0.1908</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3176</v>
+        <v>0.213</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.0222</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4579</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6082</v>
+        <v>0.8017</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1451</v>
+        <v>0.2497</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4631</v>
+        <v>0.552</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0834</v>
@@ -1780,13 +1780,13 @@
         <v>0.2053</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2119</v>
+        <v>-0.0184</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0077</v>
+        <v>0.1123</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2197</v>
+        <v>-0.1307</v>
       </c>
       <c r="V17" t="n">
         <v>0.6982</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2153</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>-0.4596</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2442</v>
+        <v>0.3925</v>
       </c>
       <c r="G18" t="n">
         <v>0.3802</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0329</v>
+        <v>0.1153</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0581</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0252</v>
+        <v>0.1734</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1786</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2333</v>
+        <v>-1.1231</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9328</v>
+        <v>-1.4052</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1661</v>
+        <v>0.2821</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5989</v>
+        <v>-0.909</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1744</v>
+        <v>-0.996</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7733</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4603</v>
+        <v>-0.5411</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1447</v>
+        <v>-0.5806</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6843</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0592</v>
+        <v>-0.3679</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.4154</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.089</v>
+        <v>0.0475</v>
       </c>
       <c r="P19" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1069</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8832</v>
+        <v>0.1626</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2237</v>
+        <v>-0.1714</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9686</v>
+        <v>-1.357</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8236</v>
+        <v>1.619</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1451</v>
+        <v>-2.9761</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.909</v>
+        <v>-0.5989</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.996</v>
+        <v>1.1744</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08699999999999999</v>
+        <v>-1.7733</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5411</v>
+        <v>1.4603</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5806</v>
+        <v>2.1447</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>-0.6843</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3679</v>
+        <v>-2.0592</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4154</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0475</v>
+        <v>-1.089</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.9831</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2558</v>
+        <v>0.5694</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5985</v>
+        <v>0.4137</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3952</v>
+        <v>-2.2906</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.047</v>
+        <v>-1.9424</v>
       </c>
       <c r="F21" t="n">
         <v>-0.3482</v>
@@ -2092,10 +2092,10 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6392</v>
+        <v>-0.5346</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1822</v>
+        <v>-0.0776</v>
       </c>
       <c r="U21" t="n">
         <v>-0.457</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2221</v>
+        <v>-4.1654</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0337</v>
+        <v>-4.0217</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1885</v>
+        <v>-0.1438</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.269</v>
+        <v>-3.2069</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8717</v>
+        <v>-1.4597</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6027</v>
+        <v>-1.7472</v>
       </c>
       <c r="J23" t="n">
-        <v>0.214</v>
+        <v>-2.4106</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4569</v>
+        <v>-0.963</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6709000000000001</v>
+        <v>-1.4476</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.483</v>
+        <v>-0.7963</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4148</v>
+        <v>-0.4967</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0682</v>
+        <v>-0.2996</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.6694</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4908</v>
+        <v>-3.0801</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>0.895</v>
+        <v>0.7458</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9413</v>
+        <v>0.2904</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0464</v>
+        <v>0.4554</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1786</v>
+        <v>0.3491</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6982</v>
+        <v>1.1786</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4805</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.208</v>
+        <v>-4.6405</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9631</v>
+        <v>-3.4521</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2449</v>
+        <v>-1.1885</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2069</v>
+        <v>-1.269</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4597</v>
+        <v>-1.8717</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7472</v>
+        <v>0.6027</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.4106</v>
+        <v>0.214</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.963</v>
+        <v>-0.4569</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4476</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7963</v>
+        <v>-1.483</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4967</v>
+        <v>-1.4148</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2996</v>
+        <v>-0.0682</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0534</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.0801</v>
+        <v>-3.4908</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2967</v>
+        <v>0.4766</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.651</v>
+        <v>0.5229</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3543</v>
+        <v>-0.0464</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3491</v>
+        <v>-1.1786</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1786</v>
+        <v>-0.6982</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8295</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.821600000000002</v>
+        <v>-4.426900000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-1.587400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.2345</v>
+        <v>-2.8398</v>
       </c>
       <c r="G25" t="n">
         <v>1.7894</v>
@@ -2389,7 +2389,7 @@
         <v>-9.028700000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.8867</v>
+        <v>-7.886699999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-1.1419</v>
@@ -2404,13 +2404,13 @@
         <v>13.3471</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9762</v>
+        <v>3.3709</v>
       </c>
       <c r="T25" t="n">
-        <v>3.543699999999999</v>
+        <v>3.5436</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.5677</v>
+        <v>-0.1729000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4269</v>
